--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.47662328603133</v>
+        <v>8.52745128398009</v>
       </c>
       <c r="D2" t="n">
-        <v>56.22438104692091</v>
+        <v>9.136461920124649</v>
       </c>
       <c r="E2" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F2" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.88089158344921</v>
+        <v>8.918144882310497</v>
       </c>
       <c r="D3" t="n">
-        <v>60.94927169786377</v>
+        <v>9.904256650902862</v>
       </c>
       <c r="E3" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F3" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.42749620635854</v>
+        <v>6.081968133533263</v>
       </c>
       <c r="D4" t="n">
-        <v>40.67823971884609</v>
+        <v>6.610213954312489</v>
       </c>
       <c r="E4" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F4" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.68837729852491</v>
+        <v>11.1618613110103</v>
       </c>
       <c r="D5" t="n">
-        <v>26.14930201687736</v>
+        <v>4.249261577742571</v>
       </c>
       <c r="E5" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F5" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.44007217527658</v>
+        <v>9.496511728482446</v>
       </c>
       <c r="D6" t="n">
-        <v>36.64446859292212</v>
+        <v>5.954726146349844</v>
       </c>
       <c r="E6" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F6" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.64735880176622</v>
+        <v>6.117695805287011</v>
       </c>
       <c r="D7" t="n">
-        <v>45.54866654589747</v>
+        <v>7.401658313708339</v>
       </c>
       <c r="E7" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F7" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.97527340738551</v>
+        <v>7.633481928700145</v>
       </c>
       <c r="D8" t="n">
-        <v>8.613828437104843</v>
+        <v>1.399747121029537</v>
       </c>
       <c r="E8" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F8" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.77297716998007</v>
+        <v>3.375608790121762</v>
       </c>
       <c r="D9" t="n">
-        <v>30.48995735800927</v>
+        <v>4.954618070676506</v>
       </c>
       <c r="E9" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F9" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.15574793423671</v>
+        <v>5.062809039313465</v>
       </c>
       <c r="D10" t="n">
-        <v>18.40123295818948</v>
+        <v>2.99020035570579</v>
       </c>
       <c r="E10" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F10" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.68637035277719</v>
+        <v>2.711535182326293</v>
       </c>
       <c r="D11" t="n">
-        <v>17.16907898591876</v>
+        <v>2.789975335211798</v>
       </c>
       <c r="E11" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F11" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.84732388555196</v>
+        <v>3.225190131402194</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30242414297965</v>
+        <v>3.136643923234193</v>
       </c>
       <c r="E12" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F12" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.83660596338289</v>
+        <v>3.22344846904972</v>
       </c>
       <c r="D13" t="n">
-        <v>15.51669435915831</v>
+        <v>2.521462833363226</v>
       </c>
       <c r="E13" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F13" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.30478065143834</v>
+        <v>5.574526855858729</v>
       </c>
       <c r="D14" t="n">
-        <v>33.52048290383686</v>
+        <v>5.44707847187349</v>
       </c>
       <c r="E14" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F14" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.6073060104103</v>
+        <v>6.273687226691675</v>
       </c>
       <c r="D15" t="n">
-        <v>31.66333931075204</v>
+        <v>5.145292637997206</v>
       </c>
       <c r="E15" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F15" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.486580316659</v>
+        <v>6.091569301457088</v>
       </c>
       <c r="D16" t="n">
-        <v>37.30303275026427</v>
+        <v>6.061742821917944</v>
       </c>
       <c r="E16" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F16" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>23.04125041322231</v>
+        <v>3.744203192148625</v>
       </c>
       <c r="D17" t="n">
-        <v>22.25948704634127</v>
+        <v>3.617166645030456</v>
       </c>
       <c r="E17" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F17" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8.097334038301319</v>
+        <v>1.315816781223965</v>
       </c>
       <c r="D18" t="n">
-        <v>8.703344317066428</v>
+        <v>1.414293451523295</v>
       </c>
       <c r="E18" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F18" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>16.82779027981615</v>
+        <v>2.734515920470124</v>
       </c>
       <c r="D19" t="n">
-        <v>17.560656371756</v>
+        <v>2.85360666041035</v>
       </c>
       <c r="E19" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F19" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>61.80766912026733</v>
+        <v>10.04374623204344</v>
       </c>
       <c r="D20" t="n">
-        <v>54.06937321947896</v>
+        <v>8.786273148165332</v>
       </c>
       <c r="E20" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F20" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>57.03700901964821</v>
+        <v>9.268513965692835</v>
       </c>
       <c r="D21" t="n">
-        <v>50.47197471339502</v>
+        <v>8.201695890926691</v>
       </c>
       <c r="E21" t="n">
-        <v>17.15518558300542</v>
+        <v>2.787717657238381</v>
       </c>
       <c r="F21" t="n">
-        <v>15.53649247299354</v>
+        <v>2.524680026861451</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
